--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -4053,7 +4053,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 46.6, "op_wape_pct": 149.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 5265.43, "rev_act": 3406.55, "op_pred": 68.09, "op_act": 37.37}, {"q": "2025Q4", "rev_pred": 5294.09, "rev_act": 3579.2, "op_pred": 68.46, "op_act": -26.11}, {"q": "2026Q1", "rev_pred": 5224.68, "rev_act": 3559.35, "op_pred": 67.56, "op_act": 10.53}, {"q": "2026Q2", "rev_pred": 5143.14, "rev_act": 3731.33, "op_pred": 66.51, "op_act": 55.59}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 46.6, "op_wape_pct": 149.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 5265.44, "rev_act": 3406.55, "op_pred": 68.09, "op_act": 37.37}, {"q": "2025Q4", "rev_pred": 5294.1, "rev_act": 3579.2, "op_pred": 68.46, "op_act": -26.11}, {"q": "2026Q1", "rev_pred": 5224.68, "rev_act": 3559.35, "op_pred": 67.56, "op_act": 10.53}, {"q": "2026Q2", "rev_pred": 5143.13, "rev_act": 3731.33, "op_pred": 66.51, "op_act": 55.59}]}</t>
         </is>
       </c>
     </row>

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$97</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$107</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$94</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -3925,7 +3925,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 46.6, "op_wape_pct": 149.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 5265.44, "rev_act": 3406.55, "op_pred": 68.09, "op_act": 37.37}, {"q": "2025Q4", "rev_pred": 5294.1, "rev_act": 3579.2, "op_pred": 68.46, "op_act": -26.11}, {"q": "2026Q1", "rev_pred": 5224.68, "rev_act": 3559.35, "op_pred": 67.56, "op_act": 10.53}, {"q": "2026Q2", "rev_pred": 5143.13, "rev_act": 3731.33, "op_pred": 66.51, "op_act": 55.59}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 53.5, "op_wape_pct": 159.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 18.3, "wape_trend": 25.5, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 5265.44, "rev_act": 3406.55, "op_pred": 68.09, "op_act": 37.37}, {"q": "2025Q4", "rev_pred": 5473.11, "rev_act": 3579.2, "op_pred": 70.77, "op_act": -26.11}, {"q": "2026Q1", "rev_pred": 5550.01, "rev_act": 3559.35, "op_pred": 71.77, "op_act": 10.53}, {"q": "2026Q2", "rev_pred": 5627.6, "rev_act": 3731.33, "op_pred": 72.77, "op_act": 55.59}]}</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO97"/>
+  <dimension ref="A1:AO107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16125,78 +16125,33 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>-2577.4</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>16441.59</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>2262.41</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>-14492.06</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>-46878.96</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>-42667.02</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>13932.01</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>-2616.03</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>-51713.01</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>43150.59</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>2753.56</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>-25950.23</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>28484.94</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>47711.35</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>-9662.969999999999</v>
-      </c>
-      <c r="U78" s="34" t="n">
-        <v>40583.09</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
       <c r="V78" s="18" t="n">
-        <v>-8473.1</v>
+        <v>270.81</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>38044.93</v>
+        <v>294.41</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>-1743.32</v>
+        <v>255.58</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>10126.43</v>
+        <v>246.9</v>
       </c>
       <c r="Z78" s="34" t="n">
-        <v>37954.94</v>
+        <v>1067.7</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>14629.84</v>
+        <v>260.7</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>48186.66</v>
+        <v>552.33</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -16218,73 +16173,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>32.28</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>32.36</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>59.05</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>30.39</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>57.84</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>179.64</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>38.97</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>77.16</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>44.23</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>44.89</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>205.25</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>67.36</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
       <c r="U79" s="9" t="n"/>
       <c r="V79" s="18" t="n">
-        <v>71.53</v>
+        <v>0</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>151.72</v>
+        <v>25.82</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>70.05</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>65.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z79" s="34" t="n">
-        <v>358.95</v>
+        <v>25.82</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>87.93000000000001</v>
+        <v>3.83</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>359.44</v>
+        <v>51.8</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -16306,38 +16221,34 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>-365.16</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>-424.32</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>-578.8</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>-590.15</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>-931.92</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>-2525.19</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>-1408.9</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>-1588.87</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
       <c r="P80" s="9" t="n"/>
       <c r="U80" s="9" t="n"/>
-      <c r="Z80" s="9" t="n"/>
-      <c r="AB80" s="5" t="n"/>
+      <c r="V80" s="18" t="n">
+        <v>1762.94</v>
+      </c>
+      <c r="W80" s="18" t="n">
+        <v>1641.54</v>
+      </c>
+      <c r="X80" s="18" t="n">
+        <v>1156.97</v>
+      </c>
+      <c r="Y80" s="18" t="n">
+        <v>1150.98</v>
+      </c>
+      <c r="Z80" s="34" t="n">
+        <v>5712.43</v>
+      </c>
+      <c r="AA80" s="18" t="n">
+        <v>1144.78</v>
+      </c>
+      <c r="AB80" s="19" t="n">
+        <v>1301.1</v>
+      </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="11" t="n"/>
@@ -16358,73 +16269,33 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>9.369999999999999</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>-251.31</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>-387.37</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>-1831.93</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>-2471.4</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>-73.22</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>1946.85</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>-41.43</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>1819.1</v>
-      </c>
-      <c r="Q81" s="18" t="n">
-        <v>-136.41</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>-87.41</v>
-      </c>
-      <c r="S81" s="18" t="n">
-        <v>-62.83</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
       <c r="V81" s="18" t="n">
-        <v>-54.87</v>
+        <v>353.48</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>71.12</v>
+        <v>340.21</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>-268.28</v>
+        <v>484.91</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>23.18</v>
+        <v>762.3099999999999</v>
       </c>
       <c r="Z81" s="34" t="n">
-        <v>-228.85</v>
+        <v>1940.91</v>
       </c>
       <c r="AA81" s="18" t="n">
-        <v>47.06</v>
+        <v>955.3</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>-105.09</v>
+        <v>493.61</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -16446,78 +16317,33 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>-3569.55</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-3725.1</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>-6078.95</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>-2654.62</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-2843.22</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-15301.89</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>-4838.45</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>-2116.5</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>-2076.94</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>-2786.99</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>-11818.88</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>2475.9</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>-1622.19</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>-976.47</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>-2017.33</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>-2140.09</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
       <c r="V82" s="18" t="n">
-        <v>-2807.31</v>
+        <v>438.45</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-4371.89</v>
+        <v>563.3099999999999</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>-3681.16</v>
+        <v>1365.47</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>-2002.61</v>
+        <v>659.89</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>-12862.97</v>
+        <v>3027.12</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>-21668.37</v>
+        <v>439.34</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>125.68</v>
+        <v>643.11</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -16539,65 +16365,33 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>39.71</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>859.58</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>48.68</v>
-      </c>
       <c r="K83" s="9" t="n"/>
-      <c r="L83" s="18" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>87.55</v>
-      </c>
-      <c r="S83" s="18" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="T83" s="18" t="n">
-        <v>112.69</v>
-      </c>
+      <c r="P83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="18" t="n">
-        <v>15.29</v>
+        <v>180.7</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>585.7</v>
+        <v>538.65</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>37.7</v>
+        <v>-262.97</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>43.35</v>
+        <v>270.51</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>682.04</v>
+        <v>726.89</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>1.27</v>
+        <v>1180.87</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>1.64</v>
+        <v>866.6</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -16619,73 +16413,33 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>5488.89</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="18" t="n">
-        <v>5364.98</v>
-      </c>
-      <c r="H84" s="18" t="n">
-        <v>5376.94</v>
-      </c>
-      <c r="I84" s="18" t="n">
-        <v>3297.9</v>
-      </c>
-      <c r="J84" s="18" t="n">
-        <v>4010.47</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>18050.29</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>4705.3</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>1746.6</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>3375.87</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>1764.25</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>11592.02</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>621.15</v>
-      </c>
-      <c r="R84" s="18" t="n">
-        <v>1363.81</v>
-      </c>
-      <c r="S84" s="18" t="n">
-        <v>1075.21</v>
-      </c>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
       <c r="U84" s="9" t="n"/>
       <c r="V84" s="18" t="n">
-        <v>2857.41</v>
+        <v>193.49</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>5186.91</v>
+        <v>2921.98</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>4664.64</v>
+        <v>-2117.5</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>3146.92</v>
+        <v>-455.43</v>
       </c>
       <c r="Z84" s="34" t="n">
-        <v>15855.88</v>
+        <v>542.54</v>
       </c>
       <c r="AA84" s="18" t="n">
-        <v>1762.85</v>
+        <v>150.62</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>1353.5</v>
+        <v>223.98</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -16707,73 +16461,33 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>5488.89</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>5364.98</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>5376.94</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>3297.9</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>4010.47</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>18050.29</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>4705.3</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>1746.6</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>3375.87</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>2786.25</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>12614.02</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>621.15</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>1363.81</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>1075.21</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
       <c r="U85" s="9" t="n"/>
       <c r="V85" s="18" t="n">
-        <v>2857.41</v>
+        <v>39.91</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>5186.91</v>
+        <v>-24.16</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>4664.64</v>
+        <v>50.03</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>3146.92</v>
+        <v>146.56</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>15855.88</v>
+        <v>212.34</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>1762.85</v>
+        <v>153.39</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>1353.5</v>
+        <v>86.73</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -16795,78 +16509,33 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>9400.950000000001</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>-16267.93</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>3699.99</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>18973.28</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>52215.73</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>58621.07</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>-5475.32</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>608.64</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>55401.75</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>-35205.63</v>
-      </c>
-      <c r="P86" s="34" t="n">
-        <v>15329.44</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>11315.08</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>-25049.62</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>462.88</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>-27498.13</v>
-      </c>
-      <c r="U86" s="34" t="n">
-        <v>-40769.79</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
       <c r="V86" s="18" t="n">
-        <v>12152.9</v>
+        <v>8.57</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>-21045.43</v>
+        <v>112.27</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>-9728.709999999999</v>
+        <v>-8.74</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>-7227.42</v>
+        <v>97.14</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>-25848.66</v>
+        <v>209.24</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>20590.9</v>
+        <v>11.77</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>-19145.47</v>
+        <v>26.66</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -16888,78 +16557,33 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>62561.58</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>17667.22</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>63492.54</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>147268.35</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>218270.02</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>446698.13</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>206880.38</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>189389.38</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>379244.75</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>277533.57</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>1053048.08</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>371083.14</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>209022.73</v>
-      </c>
-      <c r="S87" s="18" t="n">
-        <v>372295</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>172687.99</v>
-      </c>
-      <c r="U87" s="34" t="n">
-        <v>1125088.86</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="U87" s="9" t="n"/>
       <c r="V87" s="18" t="n">
-        <v>225527</v>
+        <v>-1492.13</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>206144.61</v>
+        <v>-1347.13</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>185039.98</v>
+        <v>-901.39</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>156129.55</v>
+        <v>-904.08</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>772841.14</v>
+        <v>-4644.73</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>105334</v>
+        <v>-884.08</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>44127.75</v>
+        <v>-748.77</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -16981,78 +16605,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>49532.2</v>
+        <v>-2577.4</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>30314</v>
+        <v>16441.59</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>54166</v>
+        <v>2262.41</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>124625.48</v>
+        <v>-14492.06</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>162472.68</v>
+        <v>-46878.96</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>371578.16</v>
+        <v>-42667.02</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>209043.44</v>
+        <v>13932.01</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>185400.94</v>
+        <v>-2616.03</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>320174.84</v>
+        <v>-51713.01</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>309306.22</v>
+        <v>43150.59</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>1023925.44</v>
+        <v>2753.56</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>356360.71</v>
+        <v>-25950.23</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>250759.23</v>
+        <v>28484.94</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>372610</v>
+        <v>47711.35</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>202913.64</v>
+        <v>-9662.969999999999</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>1182643.58</v>
+        <v>40583.09</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>209997</v>
+        <v>-8473.1</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>220923.51</v>
+        <v>38044.93</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>191449.01</v>
+        <v>-1743.32</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>160210.3</v>
+        <v>10126.43</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>782579.8199999999</v>
+        <v>37954.94</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>121566.9</v>
+        <v>14629.84</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>57643.01</v>
+        <v>48186.66</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -17074,33 +16698,74 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0</v>
+        <v>32.28</v>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="K89" s="9" t="n"/>
+      <c r="G89" s="18" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="H89" s="18" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="K89" s="34" t="n">
+        <v>179.64</v>
+      </c>
       <c r="L89" s="18" t="n">
-        <v>0</v>
+        <v>38.97</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="9" t="n"/>
+        <v>77.16</v>
+      </c>
+      <c r="N89" s="18" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="O89" s="18" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="P89" s="34" t="n">
+        <v>205.25</v>
+      </c>
       <c r="Q89" s="18" t="n">
-        <v>0</v>
+        <v>64.25</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0</v>
+        <v>149.1</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>0</v>
+        <v>67.36</v>
       </c>
       <c r="U89" s="9" t="n"/>
-      <c r="Z89" s="9" t="n"/>
-      <c r="AB89" s="5" t="n"/>
+      <c r="V89" s="18" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="W89" s="18" t="n">
+        <v>151.72</v>
+      </c>
+      <c r="X89" s="18" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="Y89" s="18" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="Z89" s="34" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="AA89" s="18" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="AB89" s="19" t="n">
+        <v>359.44</v>
+      </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="11" t="n"/>
@@ -17121,46 +16786,36 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0</v>
+        <v>-365.16</v>
       </c>
       <c r="F90" s="9" t="n"/>
+      <c r="G90" s="18" t="n">
+        <v>-424.32</v>
+      </c>
+      <c r="H90" s="18" t="n">
+        <v>-578.8</v>
+      </c>
       <c r="I90" s="18" t="n">
-        <v>0</v>
+        <v>-590.15</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="9" t="n"/>
+        <v>-931.92</v>
+      </c>
+      <c r="K90" s="34" t="n">
+        <v>-2525.19</v>
+      </c>
       <c r="L90" s="18" t="n">
-        <v>0</v>
+        <v>-1408.9</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>0</v>
+        <v>-1588.87</v>
       </c>
       <c r="P90" s="9" t="n"/>
-      <c r="Q90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="U90" s="9" t="n"/>
-      <c r="X90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z90" s="9" t="n"/>
       <c r="AB90" s="5" t="n"/>
       <c r="AC90" s="10" t="n"/>
@@ -17183,73 +16838,73 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>3628.43</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>3621.15</v>
+        <v>-251.31</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>3651.13</v>
+        <v>-387.37</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>3648.59</v>
+        <v>-1831.93</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>3531.61</v>
+        <v>-0.79</v>
       </c>
       <c r="K91" s="34" t="n">
-        <v>14452.48</v>
+        <v>-2471.4</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>3368.66</v>
+        <v>-73.22</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>3369.8</v>
+        <v>1946.85</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>3668.16</v>
+        <v>-13.1</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>3433.22</v>
+        <v>-41.43</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>13839.84</v>
+        <v>1819.1</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>3387.36</v>
+        <v>-136.41</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>3283.11</v>
+        <v>-87.41</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>3207.11</v>
+        <v>-62.83</v>
       </c>
       <c r="U91" s="9" t="n"/>
       <c r="V91" s="18" t="n">
-        <v>3390.1</v>
+        <v>-54.87</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>3321.23</v>
+        <v>71.12</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>3276.64</v>
+        <v>-268.28</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>3146.66</v>
+        <v>23.18</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>13134.63</v>
+        <v>-228.85</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>3106.03</v>
+        <v>47.06</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>3045.63</v>
+        <v>-105.09</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -17271,78 +16926,78 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>3209.43</v>
+        <v>-3569.55</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>-3580.31</v>
+        <v>-3725.1</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>-45.9</v>
+        <v>-6078.95</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>1892.26</v>
+        <v>-2654.62</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>2351.3</v>
+        <v>-2843.22</v>
       </c>
       <c r="K92" s="34" t="n">
-        <v>617.35</v>
+        <v>-15301.89</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>3708.83</v>
+        <v>-4838.45</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>-4291.8</v>
+        <v>-2116.5</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>1628.91</v>
+        <v>-2076.94</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>5216.22</v>
+        <v>-2786.99</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>6262.16</v>
+        <v>-11818.88</v>
       </c>
       <c r="Q92" s="18" t="n">
-        <v>-12110.69</v>
+        <v>2475.9</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1858.93</v>
+        <v>-1622.19</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>47196.83</v>
+        <v>-976.47</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>-38981.17</v>
+        <v>-2017.33</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>-2036.1</v>
+        <v>-2140.09</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>896.75</v>
+        <v>-2807.31</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>12230.97</v>
+        <v>-4371.89</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>-14931.62</v>
+        <v>-3681.16</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>990.1900000000001</v>
+        <v>-2002.61</v>
       </c>
       <c r="Z92" s="34" t="n">
-        <v>-813.71</v>
+        <v>-12862.97</v>
       </c>
       <c r="AA92" s="18" t="n">
-        <v>13889.31</v>
+        <v>-21668.37</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>30138.33</v>
+        <v>125.68</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -17364,78 +17019,65 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>3209.44</v>
+        <v>39.71</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>10698.94</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>-45.91</v>
+        <v>859.58</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>1892.27</v>
+        <v>6.18</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>2351.3</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>14896.6</v>
-      </c>
+        <v>48.68</v>
+      </c>
+      <c r="K93" s="9" t="n"/>
       <c r="L93" s="18" t="n">
-        <v>18605.43</v>
+        <v>35.85</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>-4291.81</v>
+        <v>11.21</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>1628.91</v>
+        <v>2.36</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>5216.22</v>
+        <v>38.13</v>
       </c>
       <c r="P93" s="34" t="n">
-        <v>21158.75</v>
-      </c>
-      <c r="Q93" s="18" t="n">
-        <v>9048.059999999999</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>1858.94</v>
+        <v>87.55</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>47196.82</v>
+        <v>54.18</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>-38981.16</v>
-      </c>
-      <c r="U93" s="34" t="n">
-        <v>19122.66</v>
-      </c>
+        <v>112.69</v>
+      </c>
+      <c r="U93" s="9" t="n"/>
       <c r="V93" s="18" t="n">
-        <v>20019.41</v>
+        <v>15.29</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>12230.96</v>
+        <v>585.7</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>-14931.61</v>
+        <v>37.7</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>990.1799999999999</v>
+        <v>43.35</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>18308.94</v>
+        <v>682.04</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>32198.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>30138.33</v>
+        <v>1.64</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -17457,33 +17099,74 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>5488.89</v>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>5364.98</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>5376.94</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>3297.9</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>4010.47</v>
+      </c>
+      <c r="K94" s="34" t="n">
+        <v>18050.29</v>
+      </c>
       <c r="L94" s="18" t="n">
-        <v>0</v>
+        <v>4705.3</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>0</v>
+        <v>1746.6</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" s="9" t="n"/>
+        <v>3375.87</v>
+      </c>
+      <c r="O94" s="18" t="n">
+        <v>1764.25</v>
+      </c>
+      <c r="P94" s="34" t="n">
+        <v>11592.02</v>
+      </c>
       <c r="Q94" s="18" t="n">
-        <v>0</v>
+        <v>621.15</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>0</v>
+        <v>1363.81</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>0</v>
+        <v>1075.21</v>
       </c>
       <c r="U94" s="9" t="n"/>
-      <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+      <c r="V94" s="18" t="n">
+        <v>2857.41</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>5186.91</v>
+      </c>
+      <c r="X94" s="18" t="n">
+        <v>4664.64</v>
+      </c>
+      <c r="Y94" s="18" t="n">
+        <v>3146.92</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>15855.88</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>1762.85</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>1353.5</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -17504,37 +17187,73 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>5488.89</v>
       </c>
       <c r="F95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>5364.98</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>5376.94</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>3297.9</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>4010.47</v>
+      </c>
+      <c r="K95" s="34" t="n">
+        <v>18050.29</v>
+      </c>
+      <c r="L95" s="18" t="n">
+        <v>4705.3</v>
+      </c>
+      <c r="M95" s="18" t="n">
+        <v>1746.6</v>
+      </c>
+      <c r="N95" s="18" t="n">
+        <v>3375.87</v>
+      </c>
       <c r="O95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="9" t="n"/>
+        <v>2786.25</v>
+      </c>
+      <c r="P95" s="34" t="n">
+        <v>12614.02</v>
+      </c>
       <c r="Q95" s="18" t="n">
-        <v>0</v>
+        <v>621.15</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>22.4</v>
+        <v>1363.81</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>0</v>
+        <v>1075.21</v>
       </c>
       <c r="U95" s="9" t="n"/>
+      <c r="V95" s="18" t="n">
+        <v>2857.41</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>5186.91</v>
+      </c>
       <c r="X95" s="18" t="n">
-        <v>0</v>
+        <v>4664.64</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z95" s="9" t="n"/>
+        <v>3146.92</v>
+      </c>
+      <c r="Z95" s="34" t="n">
+        <v>15855.88</v>
+      </c>
       <c r="AA95" s="18" t="n">
-        <v>3.82</v>
+        <v>1762.85</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>51.8</v>
+        <v>1353.5</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -17556,24 +17275,79 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>9400.950000000001</v>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="K96" s="9" t="n"/>
-      <c r="P96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>-16267.93</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>3699.99</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>18973.28</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>52215.73</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>58621.07</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>-5475.32</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>608.64</v>
+      </c>
+      <c r="N96" s="18" t="n">
+        <v>55401.75</v>
+      </c>
+      <c r="O96" s="18" t="n">
+        <v>-35205.63</v>
+      </c>
+      <c r="P96" s="34" t="n">
+        <v>15329.44</v>
+      </c>
       <c r="Q96" s="18" t="n">
-        <v>0</v>
+        <v>11315.08</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>0</v>
+        <v>-25049.62</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" s="9" t="n"/>
-      <c r="Z96" s="9" t="n"/>
-      <c r="AB96" s="5" t="n"/>
+        <v>462.88</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>-27498.13</v>
+      </c>
+      <c r="U96" s="34" t="n">
+        <v>-40769.79</v>
+      </c>
+      <c r="V96" s="18" t="n">
+        <v>12152.9</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>-21045.43</v>
+      </c>
+      <c r="X96" s="18" t="n">
+        <v>-9728.709999999999</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>-7227.42</v>
+      </c>
+      <c r="Z96" s="34" t="n">
+        <v>-25848.66</v>
+      </c>
+      <c r="AA96" s="18" t="n">
+        <v>20590.9</v>
+      </c>
+      <c r="AB96" s="19" t="n">
+        <v>-19145.47</v>
+      </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
       <c r="AE96" s="11" t="n"/>
@@ -17594,28 +17368,78 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>62561.58</v>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
-      <c r="P97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>17667.22</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>63492.54</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>147268.35</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>218270.02</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>446698.13</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>206880.38</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>189389.38</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>379244.75</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>277533.57</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>1053048.08</v>
+      </c>
+      <c r="Q97" s="18" t="n">
+        <v>371083.14</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>209022.73</v>
+      </c>
       <c r="S97" s="18" t="n">
-        <v>4000</v>
+        <v>372295</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>6000</v>
-      </c>
-      <c r="U97" s="9" t="n"/>
+        <v>172687.99</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>1125088.86</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>225527</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>206144.61</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>185039.98</v>
+      </c>
       <c r="Y97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z97" s="9" t="n"/>
+        <v>156129.55</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>772841.14</v>
+      </c>
       <c r="AA97" s="18" t="n">
-        <v>40000</v>
+        <v>105334</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>0</v>
+        <v>44127.75</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -17630,6 +17454,662 @@
       <c r="AM97" s="10" t="n"/>
       <c r="AN97" s="10" t="n"/>
       <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>49532.2</v>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>30314</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>54166</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>124625.48</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>162472.68</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>371578.16</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>209043.44</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>185400.94</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>320174.84</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>309306.22</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>1023925.44</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>356360.71</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>250759.23</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>372610</v>
+      </c>
+      <c r="T98" s="18" t="n">
+        <v>202913.64</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>1182643.58</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>209997</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>220923.51</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>191449.01</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>160210.3</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>782579.8199999999</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>121566.9</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>57643.01</v>
+      </c>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="K99" s="9" t="n"/>
+      <c r="L99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="9" t="n"/>
+      <c r="Q99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="9" t="n"/>
+      <c r="Z99" s="9" t="n"/>
+      <c r="AB99" s="5" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="I100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="9" t="n"/>
+      <c r="L100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="9" t="n"/>
+      <c r="Q100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" s="9" t="n"/>
+      <c r="X100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="9" t="n"/>
+      <c r="AB100" s="5" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>3628.43</v>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>3621.15</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>3651.13</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>3648.59</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>3531.61</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>14452.48</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>3368.66</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>3369.8</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>3668.16</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>3433.22</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>13839.84</v>
+      </c>
+      <c r="Q101" s="18" t="n">
+        <v>3387.36</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>3283.11</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>3207.11</v>
+      </c>
+      <c r="U101" s="9" t="n"/>
+      <c r="V101" s="18" t="n">
+        <v>3390.1</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>3321.23</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>3276.64</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>3146.66</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>13134.63</v>
+      </c>
+      <c r="AA101" s="18" t="n">
+        <v>3106.03</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>3045.63</v>
+      </c>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>3209.43</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>-3580.31</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>-45.9</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>1892.26</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>2351.3</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>617.35</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>3708.83</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>-4291.8</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>1628.91</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>5216.22</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>6262.16</v>
+      </c>
+      <c r="Q102" s="18" t="n">
+        <v>-12110.69</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>1858.93</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>47196.83</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>-38981.17</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>-2036.1</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>896.75</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>12230.97</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>-14931.62</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>990.1900000000001</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>-813.71</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>13889.31</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>30138.33</v>
+      </c>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>3209.44</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>10698.94</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>-45.91</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>1892.27</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>2351.3</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>14896.6</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>18605.43</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>-4291.81</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>1628.91</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>5216.22</v>
+      </c>
+      <c r="P103" s="34" t="n">
+        <v>21158.75</v>
+      </c>
+      <c r="Q103" s="18" t="n">
+        <v>9048.059999999999</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>1858.94</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>47196.82</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>-38981.16</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>19122.66</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>20019.41</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>12230.96</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>-14931.61</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>990.1799999999999</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>18308.94</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>32198.25</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>30138.33</v>
+      </c>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="L104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="9" t="n"/>
+      <c r="Q104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="9" t="n"/>
+      <c r="Z104" s="9" t="n"/>
+      <c r="AB104" s="5" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+      <c r="O105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="9" t="n"/>
+      <c r="Q105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="18" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="S105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="9" t="n"/>
+      <c r="X105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="9" t="n"/>
+      <c r="AA105" s="18" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB105" s="19" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+      <c r="P106" s="9" t="n"/>
+      <c r="Q106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="9" t="n"/>
+      <c r="Z106" s="9" t="n"/>
+      <c r="AB106" s="5" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="10" t="n"/>
+      <c r="AL106" s="10" t="n"/>
+      <c r="AM106" s="10" t="n"/>
+      <c r="AN106" s="10" t="n"/>
+      <c r="AO106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="n"/>
+      <c r="K107" s="9" t="n"/>
+      <c r="P107" s="9" t="n"/>
+      <c r="S107" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T107" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="U107" s="9" t="n"/>
+      <c r="Y107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="9" t="n"/>
+      <c r="AA107" s="18" t="n">
+        <v>40000</v>
+      </c>
+      <c r="AB107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="10" t="n"/>
+      <c r="AL107" s="10" t="n"/>
+      <c r="AM107" s="10" t="n"/>
+      <c r="AN107" s="10" t="n"/>
+      <c r="AO107" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17890,7 +18370,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5660</v>
+        <v>5780</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5705</v>
+        <v>5730</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5660</v>
+        <v>5780</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02265093829907015</v>
+        <v>0.02265093829907016</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.390000000000001</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="32">
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5780</v>
+        <v>5570</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5730</v>
+        <v>5660</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5780</v>
+        <v>5570</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,560원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,610원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.59</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="32">
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5570</v>
+        <v>5560</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5660</v>
+        <v>5640</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5570</v>
+        <v>5560</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,610원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,600원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.24</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.53 가 단일 검정 5% 임계 r 0.71 미달(n=8) (suppliers_mentions·시차 1·YoY·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +1/-0/+8/-3(중위 +1억) → 추정 2026Q3 +5억(차 +5억, +871%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.53 가 단일 검정 5% 임계 r 0.71 미달(n=8, n_eff=8) (suppliers_mentions·시차 1·YoY·창 8)): 전년동기 × (1+g) 추세 / 이자발생자산 이자율: 주석 연율 2.3% 가 CF 연율 1.0% 의 2.3배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +1/-0/+8/-3(중위 +1억) → 추정 2026Q3 +5억(차 +5억, +871%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02265093829907016</v>
+        <v>0.02265093829907015</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,570원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02265093829907015</v>
+        <v>0.02265093829907016</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5560</v>
+        <v>5690</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5915,7 +5915,7 @@
         <v>5100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5520</v>
+        <v>5450</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5640</v>
+        <v>5648.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5560</v>
+        <v>5690</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.23</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 53.5, "op_wape_pct": 159.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 9.8, "wape_trend": 25.5, "adopted": true, "decision": "adopted"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 5265.44, "rev_act": 3406.55, "op_pred": 68.09, "op_act": 37.37}, {"q": "2025Q4", "rev_pred": 5473.11, "rev_act": 3579.2, "op_pred": 70.77, "op_act": -26.11}, {"q": "2026Q1", "rev_pred": 5550.01, "rev_act": 3559.35, "op_pred": 71.77, "op_act": 10.53}, {"q": "2026Q2", "rev_pred": 5627.6, "rev_act": 3731.33, "op_pred": 72.77, "op_act": 55.59}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 53.5, "op_wape_pct": 159.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 9.8, "wape_trend": 25.5, "adopted": true, "decision": "adopted"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 5265.44, "rev_act": 3406.55, "op_pred": 68.09, "op_act": 37.37}, {"q": "2025Q4", "rev_pred": 5473.11, "rev_act": 3579.2, "op_pred": 70.77, "op_act": -26.11}, {"q": "2026Q1", "rev_pred": 5550.0, "rev_act": 3559.35, "op_pred": 71.77, "op_act": 10.53}, {"q": "2026Q2", "rev_pred": 5627.6, "rev_act": 3731.33, "op_pred": 72.77, "op_act": 55.59}]}</t>
         </is>
       </c>
     </row>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5690</v>
+        <v>5380</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5915,7 +5915,7 @@
         <v>5100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5450</v>
+        <v>5310</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5648.3</v>
+        <v>5604.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5690</v>
+        <v>5380</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.44</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="32">
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5380</v>
+        <v>5490</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5604.3</v>
+        <v>5591.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5380</v>
+        <v>5490</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,570원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,450원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.93</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5490</v>
+        <v>5630</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5915,7 +5915,7 @@
         <v>5100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5310</v>
+        <v>5160</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5591.2</v>
+        <v>5578.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5490</v>
+        <v>5630</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,390원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.109999999999999</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="32">
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/079430_model.xlsx
+++ b/argus/kship/models/079430_model.xlsx
@@ -3894,7 +3894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4765,35 +4765,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4884,35 +4884,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5003,35 +5003,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5122,35 +5122,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5241,35 +5241,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>5730</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5630</v>
+        <v>5170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
         <v>5830.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5578.2</v>
+        <v>5501.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5630</v>
+        <v>5170</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,390원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,340원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40290,7 +40290,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.34</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="32">
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
